--- a/questionnaire_templates/011_livestock_feed_sustainability_study_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/011_livestock_feed_sustainability_study_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'grains'}</t>
+          <t>grains</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Grains'}</t>
+          <t>Grains</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'forages'}</t>
+          <t>forages</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Forages'}</t>
+          <t>Forages</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'local_feed_mills'}</t>
+          <t>local_feed_mills</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Local feed mills'}</t>
+          <t>Local feed mills</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'national_feed_mills'}</t>
+          <t>national_feed_mills</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'National feed mills'}</t>
+          <t>National feed mills</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'organic_farming'}</t>
+          <t>organic_farming</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Organic farming'}</t>
+          <t>Organic farming</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'regenerative_agriculture'}</t>
+          <t>regenerative_agriculture</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Regenerative agriculture'}</t>
+          <t>Regenerative agriculture</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
